--- a/InputData/bldgs/BCEU/BAU Components Energy Use.xlsx
+++ b/InputData/bldgs/BCEU/BAU Components Energy Use.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-brazil-cpl/InputData/bldgs/BCEU/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD82DBE-7347-A440-88D9-175C887FC6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084D3B1F-69A3-0C4A-A770-C27B0224F50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" tabRatio="905" firstSheet="17" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
     <definedName name="Table5_A">#REF!</definedName>
     <definedName name="Table5_A_22">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -4141,119 +4141,119 @@
       </c>
       <c r="E2" s="64">
         <f>'Electricity Share'!D39</f>
-        <v>217533633997126.25</v>
+        <v>212361957705961.28</v>
       </c>
       <c r="F2" s="64">
         <f>'Electricity Share'!E39</f>
-        <v>225201608220664.78</v>
+        <v>209692745674621.88</v>
       </c>
       <c r="G2" s="64">
         <f>'Electricity Share'!F39</f>
-        <v>233987785019872.41</v>
+        <v>211919588929232.56</v>
       </c>
       <c r="H2" s="64">
         <f>'Electricity Share'!G39</f>
-        <v>242232509561776.47</v>
+        <v>213619810445754.56</v>
       </c>
       <c r="I2" s="64">
         <f>'Electricity Share'!H39</f>
-        <v>250351373358138.94</v>
+        <v>215191492574421.09</v>
       </c>
       <c r="J2" s="64">
         <f>'Electricity Share'!I39</f>
-        <v>258321015179362.22</v>
+        <v>216624810963777.91</v>
       </c>
       <c r="K2" s="64">
         <f>'Electricity Share'!J39</f>
-        <v>266125987484649.16</v>
+        <v>218242853873580.09</v>
       </c>
       <c r="L2" s="64">
         <f>'Electricity Share'!K39</f>
-        <v>273745422244841.28</v>
+        <v>220363437407559.5</v>
       </c>
       <c r="M2" s="64">
         <f>'Electricity Share'!L39</f>
-        <v>284314676867706.25</v>
+        <v>225808304055623.38</v>
       </c>
       <c r="N2" s="64">
         <f>'Electricity Share'!M39</f>
-        <v>293766625705196.06</v>
+        <v>230651411408579.12</v>
       </c>
       <c r="O2" s="64">
         <f>'Electricity Share'!N39</f>
-        <v>303186367868882.5</v>
+        <v>235442644927752.16</v>
       </c>
       <c r="P2" s="64">
         <f>'Electricity Share'!O39</f>
-        <v>312449538691928.12</v>
+        <v>239755835986655.62</v>
       </c>
       <c r="Q2" s="64">
         <f>'Electricity Share'!P39</f>
-        <v>321717483757560.5</v>
+        <v>244049995483102.59</v>
       </c>
       <c r="R2" s="64">
         <f>'Electricity Share'!Q39</f>
-        <v>330987019872428.94</v>
+        <v>248324271762157.34</v>
       </c>
       <c r="S2" s="64">
         <f>'Electricity Share'!R39</f>
-        <v>340254962170130.75</v>
+        <v>251228886835230.31</v>
       </c>
       <c r="T2" s="64">
         <f>'Electricity Share'!S39</f>
-        <v>349525797444459.31</v>
+        <v>253769940061320.91</v>
       </c>
       <c r="U2" s="64">
         <f>'Electricity Share'!T39</f>
-        <v>358788985972162.88</v>
+        <v>256277847122973.47</v>
       </c>
       <c r="V2" s="64">
         <f>'Electricity Share'!U39</f>
-        <v>368041397022518.56</v>
+        <v>258752508544971.44</v>
       </c>
       <c r="W2" s="64">
         <f>'Electricity Share'!V39</f>
-        <v>377279796753668.75</v>
+        <v>261193705444847.59</v>
       </c>
       <c r="X2" s="64">
         <f>'Electricity Share'!W39</f>
-        <v>386500819962407.94</v>
+        <v>264285768831690.81</v>
       </c>
       <c r="Y2" s="64">
         <f>'Electricity Share'!X39</f>
-        <v>395735699456581.81</v>
+        <v>267713656180515</v>
       </c>
       <c r="Z2" s="64">
         <f>'Electricity Share'!Y39</f>
-        <v>404793015387444.44</v>
+        <v>270664488623550.34</v>
       </c>
       <c r="AA2" s="64">
         <f>'Electricity Share'!Z39</f>
-        <v>413818400677492.81</v>
+        <v>273581856900857.03</v>
       </c>
       <c r="AB2" s="64">
         <f>'Electricity Share'!AA39</f>
-        <v>422808729911047.44</v>
+        <v>276465136864284.88</v>
       </c>
       <c r="AC2" s="64">
         <f>'Electricity Share'!AB39</f>
-        <v>431760893376475.5</v>
+        <v>280350748221234.28</v>
       </c>
       <c r="AD2" s="64">
         <f>'Electricity Share'!AC39</f>
-        <v>440672077524119.25</v>
+        <v>284204065708799.62</v>
       </c>
       <c r="AE2" s="64">
         <f>'Electricity Share'!AD39</f>
-        <v>449538727490702.31</v>
+        <v>288023656549555.62</v>
       </c>
       <c r="AF2" s="64">
         <f>'Electricity Share'!AE39</f>
-        <v>458357620749134.19</v>
+        <v>292155273785595</v>
       </c>
       <c r="AG2" s="64">
         <f>'Electricity Share'!AF39</f>
-        <v>467125410546822.62</v>
+        <v>295903977535979.81</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.2">
@@ -5308,119 +5308,119 @@
       </c>
       <c r="E2" s="64">
         <f>'Electricity Share'!D40</f>
-        <v>54012782860725.383</v>
+        <v>52728675095834.438</v>
       </c>
       <c r="F2" s="64">
         <f>'Electricity Share'!E40</f>
-        <v>55641684261139.32</v>
+        <v>51809832260372.188</v>
       </c>
       <c r="G2" s="64">
         <f>'Electricity Share'!F40</f>
-        <v>57653585408533.148</v>
+        <v>52216076659878.148</v>
       </c>
       <c r="H2" s="64">
         <f>'Electricity Share'!G40</f>
-        <v>59570623253035.586</v>
+        <v>52534093258046.148</v>
       </c>
       <c r="I2" s="64">
         <f>'Electricity Share'!H40</f>
-        <v>61461906061502.641</v>
+        <v>52830064898118.656</v>
       </c>
       <c r="J2" s="64">
         <f>'Electricity Share'!I40</f>
-        <v>63322720564718.414</v>
+        <v>53101650914927.797</v>
       </c>
       <c r="K2" s="64">
         <f>'Electricity Share'!J40</f>
-        <v>65150322403381.18</v>
+        <v>53428048972173.062</v>
       </c>
       <c r="L2" s="64">
         <f>'Electricity Share'!K40</f>
-        <v>66940710336005.938</v>
+        <v>53886873837664.703</v>
       </c>
       <c r="M2" s="64">
         <f>'Electricity Share'!L40</f>
-        <v>69460857010720.484</v>
+        <v>55167177764583.789</v>
       </c>
       <c r="N2" s="64">
         <f>'Electricity Share'!M40</f>
-        <v>71717066129305.766</v>
+        <v>56308787579589.898</v>
       </c>
       <c r="O2" s="64">
         <f>'Electricity Share'!N40</f>
-        <v>73963390166544.062</v>
+        <v>57437068595925.242</v>
       </c>
       <c r="P2" s="64">
         <f>'Electricity Share'!O40</f>
-        <v>76173054173153.875</v>
+        <v>58450828122195.977</v>
       </c>
       <c r="Q2" s="64">
         <f>'Electricity Share'!P40</f>
-        <v>78397161061854.453</v>
+        <v>59470895332041.516</v>
       </c>
       <c r="R2" s="64">
         <f>'Electricity Share'!Q40</f>
-        <v>80636031481231.25</v>
+        <v>60497489608761.312</v>
       </c>
       <c r="S2" s="64">
         <f>'Electricity Share'!R40</f>
-        <v>82889992409416.797</v>
+        <v>61202224326080.789</v>
       </c>
       <c r="T2" s="64">
         <f>'Electricity Share'!S40</f>
-        <v>85161248704978.312</v>
+        <v>61830529069442.141</v>
       </c>
       <c r="U2" s="64">
         <f>'Electricity Share'!T40</f>
-        <v>87448355987937.312</v>
+        <v>62463111419955.227</v>
       </c>
       <c r="V2" s="64">
         <f>'Electricity Share'!U40</f>
-        <v>89751687506275.688</v>
+        <v>63100168829574.023</v>
       </c>
       <c r="W2" s="64">
         <f>'Electricity Share'!V40</f>
-        <v>92071605911972.734</v>
+        <v>63741881015981.117</v>
       </c>
       <c r="X2" s="64">
         <f>'Electricity Share'!W40</f>
-        <v>94408458194341.453</v>
+        <v>64555650775935.875</v>
       </c>
       <c r="Y2" s="64">
         <f>'Electricity Share'!X40</f>
-        <v>96720047825911.406</v>
+        <v>65430734869220.203</v>
       </c>
       <c r="Z2" s="64">
         <f>'Electricity Share'!Y40</f>
-        <v>99012610664780.656</v>
+        <v>66204693791998.617</v>
       </c>
       <c r="AA2" s="64">
         <f>'Electricity Share'!Z40</f>
-        <v>101322838228081.03</v>
+        <v>66986122858531.508</v>
       </c>
       <c r="AB2" s="64">
         <f>'Electricity Share'!AA40</f>
-        <v>103651087561651.23</v>
+        <v>67775119295414.398</v>
       </c>
       <c r="AC2" s="64">
         <f>'Electricity Share'!AB40</f>
-        <v>105997722915388.11</v>
+        <v>68826383734491.398</v>
       </c>
       <c r="AD2" s="64">
         <f>'Electricity Share'!AC40</f>
-        <v>108363186131627.22</v>
+        <v>69887019492589.125</v>
       </c>
       <c r="AE2" s="64">
         <f>'Electricity Share'!AD40</f>
-        <v>110747743098033.17</v>
+        <v>70957112193111.469</v>
       </c>
       <c r="AF2" s="64">
         <f>'Electricity Share'!AE40</f>
-        <v>113151748423170.16</v>
+        <v>72122461901823.828</v>
       </c>
       <c r="AG2" s="64">
         <f>'Electricity Share'!AF40</f>
-        <v>115575534513124.08</v>
+        <v>73212160152551.469</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.2">
@@ -6470,119 +6470,119 @@
       </c>
       <c r="E2" s="67">
         <f>'Electricity Share'!D41</f>
-        <v>401453583142148.38</v>
+        <v>391909367198204.31</v>
       </c>
       <c r="F2" s="67">
         <f>'Electricity Share'!E41</f>
-        <v>416156707518195.81</v>
+        <v>387497422065005.88</v>
       </c>
       <c r="G2" s="67">
         <f>'Electricity Share'!F41</f>
-        <v>429358629571594.44</v>
+        <v>388864334410889.31</v>
       </c>
       <c r="H2" s="67">
         <f>'Electricity Share'!G41</f>
-        <v>443196867185187.94</v>
+        <v>390846096296199.31</v>
       </c>
       <c r="I2" s="67">
         <f>'Electricity Share'!H41</f>
-        <v>457186720580358.44</v>
+        <v>392978442527460.25</v>
       </c>
       <c r="J2" s="67">
         <f>'Electricity Share'!I41</f>
-        <v>471356264255919.31</v>
+        <v>395273538121294.25</v>
       </c>
       <c r="K2" s="67">
         <f>'Electricity Share'!J41</f>
-        <v>485723690111969.69</v>
+        <v>398329097154246.88</v>
       </c>
       <c r="L2" s="67">
         <f>'Electricity Share'!K41</f>
-        <v>500313867419152.75</v>
+        <v>402749688754775.75</v>
       </c>
       <c r="M2" s="67">
         <f>'Electricity Share'!L41</f>
-        <v>511224466121573.19</v>
+        <v>406024518179792.81</v>
       </c>
       <c r="N2" s="67">
         <f>'Electricity Share'!M41</f>
-        <v>523516308165498.19</v>
+        <v>411039801011830.94</v>
       </c>
       <c r="O2" s="67">
         <f>'Electricity Share'!N41</f>
-        <v>535850241964573.5</v>
+        <v>416120286476322.69</v>
       </c>
       <c r="P2" s="67">
         <f>'Electricity Share'!O41</f>
-        <v>548377407134918</v>
+        <v>420793335891148.44</v>
       </c>
       <c r="Q2" s="67">
         <f>'Electricity Share'!P41</f>
-        <v>560885355180585.19</v>
+        <v>425479109184856</v>
       </c>
       <c r="R2" s="67">
         <f>'Electricity Share'!Q41</f>
-        <v>573376948646339.75</v>
+        <v>430178238629081.31</v>
       </c>
       <c r="S2" s="67">
         <f>'Electricity Share'!R41</f>
-        <v>585855045420452.5</v>
+        <v>432568888838688.88</v>
       </c>
       <c r="T2" s="67">
         <f>'Electricity Share'!S41</f>
-        <v>598312953850562.38</v>
+        <v>434399530869236.94</v>
       </c>
       <c r="U2" s="67">
         <f>'Electricity Share'!T41</f>
-        <v>610762658039900</v>
+        <v>436259041457071.44</v>
       </c>
       <c r="V2" s="67">
         <f>'Electricity Share'!U41</f>
-        <v>623206915471205.75</v>
+        <v>438147322625454.56</v>
       </c>
       <c r="W2" s="67">
         <f>'Electricity Share'!V41</f>
-        <v>635648597334358.38</v>
+        <v>440064413539171.19</v>
       </c>
       <c r="X2" s="67">
         <f>'Electricity Share'!W41</f>
-        <v>648090721843250.62</v>
+        <v>443158580392373.31</v>
       </c>
       <c r="Y2" s="67">
         <f>'Electricity Share'!X41</f>
-        <v>660544252717506.88</v>
+        <v>446855608950264.88</v>
       </c>
       <c r="Z2" s="67">
         <f>'Electricity Share'!Y41</f>
-        <v>673194373947774.88</v>
+        <v>450130817584451</v>
       </c>
       <c r="AA2" s="67">
         <f>'Electricity Share'!Z41</f>
-        <v>685858761094426</v>
+        <v>453432020240611.38</v>
       </c>
       <c r="AB2" s="67">
         <f>'Electricity Share'!AA41</f>
-        <v>698540182527301.5</v>
+        <v>456759743840300.81</v>
       </c>
       <c r="AC2" s="67">
         <f>'Electricity Share'!AB41</f>
-        <v>711241383708136.5</v>
+        <v>461822868044274.38</v>
       </c>
       <c r="AD2" s="67">
         <f>'Electricity Share'!AC41</f>
-        <v>723964736344253.5</v>
+        <v>466908914798611.25</v>
       </c>
       <c r="AE2" s="67">
         <f>'Electricity Share'!AD41</f>
-        <v>736713529411264.62</v>
+        <v>472019231257333</v>
       </c>
       <c r="AF2" s="67">
         <f>'Electricity Share'!AE41</f>
-        <v>749490630827695.5</v>
+        <v>477722264312581.12</v>
       </c>
       <c r="AG2" s="67">
         <f>'Electricity Share'!AF41</f>
-        <v>762299054940053.25</v>
+        <v>482883862311468.62</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.2">
@@ -23166,120 +23166,91 @@
         <v>649000000000000</v>
       </c>
       <c r="D33" s="69">
-        <f>_xlfn.FORECAST.LINEAR(D32,$B$33:$C$33,$B$32:$C$32)</f>
-        <v>673000000000000</v>
+        <v>657000000000000</v>
       </c>
       <c r="E33" s="69">
-        <f t="shared" ref="E33:AF33" si="6">_xlfn.FORECAST.LINEAR(E32,$B$33:$C$33,$B$32:$C$32)</f>
-        <v>697000000000000</v>
+        <v>649000000000000</v>
       </c>
       <c r="F33" s="69">
-        <f t="shared" si="6"/>
-        <v>721000000000000</v>
+        <v>653000000000000</v>
       </c>
       <c r="G33" s="69">
-        <f t="shared" si="6"/>
+        <v>657000000000000</v>
+      </c>
+      <c r="H33" s="69">
+        <v>661000000000000</v>
+      </c>
+      <c r="I33" s="69">
+        <v>665000000000000</v>
+      </c>
+      <c r="J33" s="69">
+        <v>670000000000000</v>
+      </c>
+      <c r="K33" s="69">
+        <v>677000000000000</v>
+      </c>
+      <c r="L33" s="69">
+        <v>687000000000000</v>
+      </c>
+      <c r="M33" s="69">
+        <v>698000000000000</v>
+      </c>
+      <c r="N33" s="69">
+        <v>709000000000000</v>
+      </c>
+      <c r="O33" s="69">
+        <v>719000000000000</v>
+      </c>
+      <c r="P33" s="69">
+        <v>729000000000000</v>
+      </c>
+      <c r="Q33" s="69">
+        <v>739000000000000</v>
+      </c>
+      <c r="R33" s="69">
         <v>745000000000000</v>
       </c>
-      <c r="H33" s="69">
-        <f t="shared" si="6"/>
-        <v>769000000000000</v>
-      </c>
-      <c r="I33" s="69">
-        <f t="shared" si="6"/>
-        <v>793000000000000</v>
-      </c>
-      <c r="J33" s="69">
-        <f t="shared" si="6"/>
-        <v>817000000000000</v>
-      </c>
-      <c r="K33" s="69">
-        <f t="shared" si="6"/>
-        <v>841000000000000</v>
-      </c>
-      <c r="L33" s="69">
-        <f t="shared" si="6"/>
-        <v>865000000000000</v>
-      </c>
-      <c r="M33" s="69">
-        <f t="shared" si="6"/>
-        <v>889000000000000</v>
-      </c>
-      <c r="N33" s="69">
-        <f t="shared" si="6"/>
-        <v>913000000000000</v>
-      </c>
-      <c r="O33" s="69">
-        <f t="shared" si="6"/>
-        <v>937000000000000</v>
-      </c>
-      <c r="P33" s="69">
-        <f t="shared" si="6"/>
-        <v>961000000000000</v>
-      </c>
-      <c r="Q33" s="69">
-        <f t="shared" si="6"/>
-        <v>985000000000000</v>
-      </c>
-      <c r="R33" s="69">
-        <f t="shared" si="6"/>
-        <v>1009000000000000</v>
-      </c>
       <c r="S33" s="69">
-        <f t="shared" si="6"/>
-        <v>1033000000000000</v>
+        <v>750000000000000</v>
       </c>
       <c r="T33" s="69">
-        <f t="shared" si="6"/>
-        <v>1057000000000000</v>
+        <v>755000000000000</v>
       </c>
       <c r="U33" s="69">
-        <f t="shared" si="6"/>
-        <v>1081000000000000</v>
+        <v>760000000000000</v>
       </c>
       <c r="V33" s="69">
-        <f t="shared" si="6"/>
-        <v>1105000000000000</v>
+        <v>765000000000000</v>
       </c>
       <c r="W33" s="69">
-        <f t="shared" si="6"/>
-        <v>1129000000000000</v>
+        <v>772000000000000</v>
       </c>
       <c r="X33" s="69">
-        <f t="shared" si="6"/>
-        <v>1153000000000000</v>
+        <v>780000000000000</v>
       </c>
       <c r="Y33" s="69">
-        <f t="shared" si="6"/>
-        <v>1177000000000000</v>
+        <v>787000000000000</v>
       </c>
       <c r="Z33" s="69">
-        <f t="shared" si="6"/>
-        <v>1201000000000000</v>
+        <v>794000000000000</v>
       </c>
       <c r="AA33" s="69">
-        <f t="shared" si="6"/>
-        <v>1225000000000000</v>
+        <v>801000000000000</v>
       </c>
       <c r="AB33" s="69">
-        <f t="shared" si="6"/>
-        <v>1249000000000000</v>
+        <v>811000000000000</v>
       </c>
       <c r="AC33" s="69">
-        <f t="shared" si="6"/>
-        <v>1273000000000000</v>
+        <v>821000000000000</v>
       </c>
       <c r="AD33" s="69">
-        <f t="shared" si="6"/>
-        <v>1297000000000000</v>
+        <v>831000000000000</v>
       </c>
       <c r="AE33" s="69">
-        <f t="shared" si="6"/>
-        <v>1321000000000000</v>
+        <v>842000000000000</v>
       </c>
       <c r="AF33" s="69">
-        <f t="shared" si="6"/>
-        <v>1345000000000000</v>
+        <v>852000000000000</v>
       </c>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.2">
@@ -23293,120 +23264,91 @@
         <v>570000000000000</v>
       </c>
       <c r="D34" s="69">
-        <f>_xlfn.FORECAST.LINEAR(D32,$B$34:$C$34,$B$32:$C$32)</f>
-        <v>605000000000000</v>
+        <v>591000000000000</v>
       </c>
       <c r="E34" s="69">
-        <f t="shared" ref="E34:AF34" si="7">_xlfn.FORECAST.LINEAR(E32,$B$34:$C$34,$B$32:$C$32)</f>
-        <v>640000000000000</v>
+        <v>596000000000000</v>
       </c>
       <c r="F34" s="69">
-        <f t="shared" si="7"/>
-        <v>675000000000000</v>
+        <v>604000000000000</v>
       </c>
       <c r="G34" s="69">
-        <f t="shared" si="7"/>
-        <v>710000000000000</v>
+        <v>616000000000000</v>
       </c>
       <c r="H34" s="69">
-        <f t="shared" si="7"/>
-        <v>745000000000000</v>
+        <v>626000000000000</v>
       </c>
       <c r="I34" s="69">
-        <f t="shared" si="7"/>
-        <v>780000000000000</v>
+        <v>636000000000000</v>
       </c>
       <c r="J34" s="69">
-        <f t="shared" si="7"/>
-        <v>815000000000000</v>
+        <v>647000000000000</v>
       </c>
       <c r="K34" s="69">
-        <f t="shared" si="7"/>
-        <v>850000000000000</v>
+        <v>658000000000000</v>
       </c>
       <c r="L34" s="69">
-        <f t="shared" si="7"/>
-        <v>885000000000000</v>
+        <v>668000000000000</v>
       </c>
       <c r="M34" s="69">
-        <f t="shared" si="7"/>
-        <v>920000000000000</v>
+        <v>678000000000000</v>
       </c>
       <c r="N34" s="69">
-        <f t="shared" si="7"/>
-        <v>955000000000000</v>
+        <v>687000000000000</v>
       </c>
       <c r="O34" s="69">
-        <f t="shared" si="7"/>
-        <v>990000000000000</v>
+        <v>696000000000000</v>
       </c>
       <c r="P34" s="69">
-        <f t="shared" si="7"/>
-        <v>1025000000000000</v>
+        <v>705000000000000</v>
       </c>
       <c r="Q34" s="69">
-        <f t="shared" si="7"/>
-        <v>1060000000000000</v>
+        <v>712000000000000</v>
       </c>
       <c r="R34" s="69">
-        <f t="shared" si="7"/>
-        <v>1095000000000000</v>
+        <v>716000000000000</v>
       </c>
       <c r="S34" s="69">
-        <f t="shared" si="7"/>
-        <v>1130000000000000</v>
+        <v>719000000000000</v>
       </c>
       <c r="T34" s="69">
-        <f t="shared" si="7"/>
-        <v>1165000000000000</v>
+        <v>721000000000000</v>
       </c>
       <c r="U34" s="69">
-        <f t="shared" si="7"/>
-        <v>1200000000000000</v>
+        <v>724000000000000</v>
       </c>
       <c r="V34" s="69">
-        <f t="shared" si="7"/>
-        <v>1235000000000000</v>
+        <v>726000000000000</v>
       </c>
       <c r="W34" s="69">
-        <f t="shared" si="7"/>
-        <v>1270000000000000</v>
+        <v>730000000000000</v>
       </c>
       <c r="X34" s="69">
-        <f t="shared" si="7"/>
-        <v>1305000000000000</v>
+        <v>734000000000000</v>
       </c>
       <c r="Y34" s="69">
-        <f t="shared" si="7"/>
-        <v>1340000000000000</v>
+        <v>737000000000000</v>
       </c>
       <c r="Z34" s="69">
-        <f t="shared" si="7"/>
-        <v>1375000000000000</v>
+        <v>740000000000000</v>
       </c>
       <c r="AA34" s="69">
-        <f t="shared" si="7"/>
-        <v>1410000000000000</v>
+        <v>743000000000000</v>
       </c>
       <c r="AB34" s="69">
-        <f t="shared" si="7"/>
-        <v>1445000000000000</v>
+        <v>748000000000000</v>
       </c>
       <c r="AC34" s="69">
-        <f t="shared" si="7"/>
-        <v>1480000000000000</v>
+        <v>752000000000000</v>
       </c>
       <c r="AD34" s="69">
-        <f t="shared" si="7"/>
-        <v>1515000000000000</v>
+        <v>757000000000000</v>
       </c>
       <c r="AE34" s="69">
-        <f t="shared" si="7"/>
-        <v>1550000000000000</v>
+        <v>761000000000000</v>
       </c>
       <c r="AF34" s="69">
-        <f t="shared" si="7"/>
-        <v>1585000000000000</v>
+        <v>766000000000000</v>
       </c>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.2">
@@ -23516,123 +23458,123 @@
         <v>0</v>
       </c>
       <c r="C38" s="64">
-        <f t="shared" ref="C38:AF42" si="8">C18*C$33</f>
+        <f t="shared" ref="C38:AF42" si="6">C18*C$33</f>
         <v>0</v>
       </c>
       <c r="D38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="V38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="X38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Y38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AA38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AF38" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -23641,128 +23583,128 @@
         <v>74</v>
       </c>
       <c r="B39" s="64">
-        <f t="shared" ref="B39:Q42" si="9">B19*B$33</f>
+        <f t="shared" ref="B39:Q42" si="7">B19*B$33</f>
         <v>200784554163188.62</v>
       </c>
       <c r="C39" s="64">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>207742974145950.22</v>
       </c>
       <c r="D39" s="64">
-        <f t="shared" si="9"/>
-        <v>217533633997126.25</v>
+        <f t="shared" si="7"/>
+        <v>212361957705961.28</v>
       </c>
       <c r="E39" s="64">
-        <f t="shared" si="9"/>
-        <v>225201608220664.78</v>
+        <f t="shared" si="7"/>
+        <v>209692745674621.88</v>
       </c>
       <c r="F39" s="64">
-        <f t="shared" si="9"/>
-        <v>233987785019872.41</v>
+        <f t="shared" si="7"/>
+        <v>211919588929232.56</v>
       </c>
       <c r="G39" s="64">
-        <f t="shared" si="9"/>
-        <v>242232509561776.47</v>
+        <f t="shared" si="7"/>
+        <v>213619810445754.56</v>
       </c>
       <c r="H39" s="64">
-        <f t="shared" si="9"/>
-        <v>250351373358138.94</v>
+        <f t="shared" si="7"/>
+        <v>215191492574421.09</v>
       </c>
       <c r="I39" s="64">
-        <f t="shared" si="9"/>
-        <v>258321015179362.22</v>
+        <f t="shared" si="7"/>
+        <v>216624810963777.91</v>
       </c>
       <c r="J39" s="64">
-        <f t="shared" si="9"/>
-        <v>266125987484649.16</v>
+        <f t="shared" si="7"/>
+        <v>218242853873580.09</v>
       </c>
       <c r="K39" s="64">
-        <f t="shared" si="9"/>
-        <v>273745422244841.28</v>
+        <f t="shared" si="7"/>
+        <v>220363437407559.5</v>
       </c>
       <c r="L39" s="64">
-        <f t="shared" si="9"/>
-        <v>284314676867706.25</v>
+        <f t="shared" si="7"/>
+        <v>225808304055623.38</v>
       </c>
       <c r="M39" s="64">
-        <f t="shared" si="9"/>
-        <v>293766625705196.06</v>
+        <f t="shared" si="7"/>
+        <v>230651411408579.12</v>
       </c>
       <c r="N39" s="64">
-        <f t="shared" si="9"/>
-        <v>303186367868882.5</v>
+        <f t="shared" si="7"/>
+        <v>235442644927752.16</v>
       </c>
       <c r="O39" s="64">
-        <f t="shared" si="9"/>
-        <v>312449538691928.12</v>
+        <f t="shared" si="7"/>
+        <v>239755835986655.62</v>
       </c>
       <c r="P39" s="64">
-        <f t="shared" si="9"/>
-        <v>321717483757560.5</v>
+        <f t="shared" si="7"/>
+        <v>244049995483102.59</v>
       </c>
       <c r="Q39" s="64">
-        <f t="shared" si="9"/>
-        <v>330987019872428.94</v>
+        <f t="shared" si="7"/>
+        <v>248324271762157.34</v>
       </c>
       <c r="R39" s="64">
-        <f t="shared" si="8"/>
-        <v>340254962170130.75</v>
+        <f t="shared" si="6"/>
+        <v>251228886835230.31</v>
       </c>
       <c r="S39" s="64">
-        <f t="shared" si="8"/>
-        <v>349525797444459.31</v>
+        <f t="shared" si="6"/>
+        <v>253769940061320.91</v>
       </c>
       <c r="T39" s="64">
-        <f t="shared" si="8"/>
-        <v>358788985972162.88</v>
+        <f t="shared" si="6"/>
+        <v>256277847122973.47</v>
       </c>
       <c r="U39" s="64">
-        <f t="shared" si="8"/>
-        <v>368041397022518.56</v>
+        <f t="shared" si="6"/>
+        <v>258752508544971.44</v>
       </c>
       <c r="V39" s="64">
-        <f t="shared" si="8"/>
-        <v>377279796753668.75</v>
+        <f t="shared" si="6"/>
+        <v>261193705444847.59</v>
       </c>
       <c r="W39" s="64">
-        <f t="shared" si="8"/>
-        <v>386500819962407.94</v>
+        <f t="shared" si="6"/>
+        <v>264285768831690.81</v>
       </c>
       <c r="X39" s="64">
-        <f t="shared" si="8"/>
-        <v>395735699456581.81</v>
+        <f t="shared" si="6"/>
+        <v>267713656180515</v>
       </c>
       <c r="Y39" s="64">
-        <f t="shared" si="8"/>
-        <v>404793015387444.44</v>
+        <f t="shared" si="6"/>
+        <v>270664488623550.34</v>
       </c>
       <c r="Z39" s="64">
-        <f t="shared" si="8"/>
-        <v>413818400677492.81</v>
+        <f t="shared" si="6"/>
+        <v>273581856900857.03</v>
       </c>
       <c r="AA39" s="64">
-        <f t="shared" si="8"/>
-        <v>422808729911047.44</v>
+        <f t="shared" si="6"/>
+        <v>276465136864284.88</v>
       </c>
       <c r="AB39" s="64">
-        <f t="shared" si="8"/>
-        <v>431760893376475.5</v>
+        <f t="shared" si="6"/>
+        <v>280350748221234.28</v>
       </c>
       <c r="AC39" s="64">
-        <f t="shared" si="8"/>
-        <v>440672077524119.25</v>
+        <f t="shared" si="6"/>
+        <v>284204065708799.62</v>
       </c>
       <c r="AD39" s="64">
-        <f t="shared" si="8"/>
-        <v>449538727490702.31</v>
+        <f t="shared" si="6"/>
+        <v>288023656549555.62</v>
       </c>
       <c r="AE39" s="64">
-        <f t="shared" si="8"/>
-        <v>458357620749134.19</v>
+        <f t="shared" si="6"/>
+        <v>292155273785595</v>
       </c>
       <c r="AF39" s="64">
-        <f t="shared" si="8"/>
-        <v>467125410546822.62</v>
+        <f t="shared" si="6"/>
+        <v>295903977535979.81</v>
       </c>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.2">
@@ -23770,128 +23712,128 @@
         <v>76</v>
       </c>
       <c r="B40" s="64">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>50698249679844.008</v>
       </c>
       <c r="C40" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>51958190398418.898</v>
       </c>
       <c r="D40" s="64">
-        <f t="shared" si="8"/>
-        <v>54012782860725.383</v>
+        <f t="shared" si="6"/>
+        <v>52728675095834.438</v>
       </c>
       <c r="E40" s="64">
-        <f t="shared" si="8"/>
-        <v>55641684261139.32</v>
+        <f t="shared" si="6"/>
+        <v>51809832260372.188</v>
       </c>
       <c r="F40" s="64">
-        <f t="shared" si="8"/>
-        <v>57653585408533.148</v>
+        <f t="shared" si="6"/>
+        <v>52216076659878.148</v>
       </c>
       <c r="G40" s="64">
-        <f t="shared" si="8"/>
-        <v>59570623253035.586</v>
+        <f t="shared" si="6"/>
+        <v>52534093258046.148</v>
       </c>
       <c r="H40" s="64">
-        <f t="shared" si="8"/>
-        <v>61461906061502.641</v>
+        <f t="shared" si="6"/>
+        <v>52830064898118.656</v>
       </c>
       <c r="I40" s="64">
-        <f t="shared" si="8"/>
-        <v>63322720564718.414</v>
+        <f t="shared" si="6"/>
+        <v>53101650914927.797</v>
       </c>
       <c r="J40" s="64">
-        <f t="shared" si="8"/>
-        <v>65150322403381.18</v>
+        <f t="shared" si="6"/>
+        <v>53428048972173.062</v>
       </c>
       <c r="K40" s="64">
-        <f t="shared" si="8"/>
-        <v>66940710336005.938</v>
+        <f t="shared" si="6"/>
+        <v>53886873837664.703</v>
       </c>
       <c r="L40" s="64">
-        <f t="shared" si="8"/>
-        <v>69460857010720.484</v>
+        <f t="shared" si="6"/>
+        <v>55167177764583.789</v>
       </c>
       <c r="M40" s="64">
-        <f t="shared" si="8"/>
-        <v>71717066129305.766</v>
+        <f t="shared" si="6"/>
+        <v>56308787579589.898</v>
       </c>
       <c r="N40" s="64">
-        <f t="shared" si="8"/>
-        <v>73963390166544.062</v>
+        <f t="shared" si="6"/>
+        <v>57437068595925.242</v>
       </c>
       <c r="O40" s="64">
-        <f t="shared" si="8"/>
-        <v>76173054173153.875</v>
+        <f t="shared" si="6"/>
+        <v>58450828122195.977</v>
       </c>
       <c r="P40" s="64">
-        <f t="shared" si="8"/>
-        <v>78397161061854.453</v>
+        <f t="shared" si="6"/>
+        <v>59470895332041.516</v>
       </c>
       <c r="Q40" s="64">
-        <f t="shared" si="8"/>
-        <v>80636031481231.25</v>
+        <f t="shared" si="6"/>
+        <v>60497489608761.312</v>
       </c>
       <c r="R40" s="64">
-        <f t="shared" si="8"/>
-        <v>82889992409416.797</v>
+        <f t="shared" si="6"/>
+        <v>61202224326080.789</v>
       </c>
       <c r="S40" s="64">
-        <f t="shared" si="8"/>
-        <v>85161248704978.312</v>
+        <f t="shared" si="6"/>
+        <v>61830529069442.141</v>
       </c>
       <c r="T40" s="64">
-        <f t="shared" si="8"/>
-        <v>87448355987937.312</v>
+        <f t="shared" si="6"/>
+        <v>62463111419955.227</v>
       </c>
       <c r="U40" s="64">
-        <f t="shared" si="8"/>
-        <v>89751687506275.688</v>
+        <f t="shared" si="6"/>
+        <v>63100168829574.023</v>
       </c>
       <c r="V40" s="64">
-        <f t="shared" si="8"/>
-        <v>92071605911972.734</v>
+        <f t="shared" si="6"/>
+        <v>63741881015981.117</v>
       </c>
       <c r="W40" s="64">
-        <f t="shared" si="8"/>
-        <v>94408458194341.453</v>
+        <f t="shared" si="6"/>
+        <v>64555650775935.875</v>
       </c>
       <c r="X40" s="64">
-        <f t="shared" si="8"/>
-        <v>96720047825911.406</v>
+        <f t="shared" si="6"/>
+        <v>65430734869220.203</v>
       </c>
       <c r="Y40" s="64">
-        <f t="shared" si="8"/>
-        <v>99012610664780.656</v>
+        <f t="shared" si="6"/>
+        <v>66204693791998.617</v>
       </c>
       <c r="Z40" s="64">
-        <f t="shared" si="8"/>
-        <v>101322838228081.03</v>
+        <f t="shared" si="6"/>
+        <v>66986122858531.508</v>
       </c>
       <c r="AA40" s="64">
-        <f t="shared" si="8"/>
-        <v>103651087561651.23</v>
+        <f t="shared" si="6"/>
+        <v>67775119295414.398</v>
       </c>
       <c r="AB40" s="64">
-        <f t="shared" si="8"/>
-        <v>105997722915388.11</v>
+        <f t="shared" si="6"/>
+        <v>68826383734491.398</v>
       </c>
       <c r="AC40" s="64">
-        <f t="shared" si="8"/>
-        <v>108363186131627.22</v>
+        <f t="shared" si="6"/>
+        <v>69887019492589.125</v>
       </c>
       <c r="AD40" s="64">
-        <f t="shared" si="8"/>
-        <v>110747743098033.17</v>
+        <f t="shared" si="6"/>
+        <v>70957112193111.469</v>
       </c>
       <c r="AE40" s="64">
-        <f t="shared" si="8"/>
-        <v>113151748423170.16</v>
+        <f t="shared" si="6"/>
+        <v>72122461901823.828</v>
       </c>
       <c r="AF40" s="64">
-        <f t="shared" si="8"/>
-        <v>115575534513124.08</v>
+        <f t="shared" si="6"/>
+        <v>73212160152551.469</v>
       </c>
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.2">
@@ -23899,128 +23841,128 @@
         <v>152</v>
       </c>
       <c r="B41" s="64">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>373517196156967.38</v>
       </c>
       <c r="C41" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>389298835455630.94</v>
       </c>
       <c r="D41" s="64">
-        <f t="shared" si="8"/>
-        <v>401453583142148.38</v>
+        <f t="shared" si="6"/>
+        <v>391909367198204.31</v>
       </c>
       <c r="E41" s="64">
-        <f t="shared" si="8"/>
-        <v>416156707518195.81</v>
+        <f t="shared" si="6"/>
+        <v>387497422065005.88</v>
       </c>
       <c r="F41" s="64">
-        <f t="shared" si="8"/>
-        <v>429358629571594.44</v>
+        <f t="shared" si="6"/>
+        <v>388864334410889.31</v>
       </c>
       <c r="G41" s="64">
-        <f t="shared" si="8"/>
-        <v>443196867185187.94</v>
+        <f t="shared" si="6"/>
+        <v>390846096296199.31</v>
       </c>
       <c r="H41" s="64">
-        <f t="shared" si="8"/>
-        <v>457186720580358.44</v>
+        <f t="shared" si="6"/>
+        <v>392978442527460.25</v>
       </c>
       <c r="I41" s="64">
-        <f t="shared" si="8"/>
-        <v>471356264255919.31</v>
+        <f t="shared" si="6"/>
+        <v>395273538121294.25</v>
       </c>
       <c r="J41" s="64">
-        <f t="shared" si="8"/>
-        <v>485723690111969.69</v>
+        <f t="shared" si="6"/>
+        <v>398329097154246.88</v>
       </c>
       <c r="K41" s="64">
-        <f t="shared" si="8"/>
-        <v>500313867419152.75</v>
+        <f t="shared" si="6"/>
+        <v>402749688754775.75</v>
       </c>
       <c r="L41" s="64">
-        <f t="shared" si="8"/>
-        <v>511224466121573.19</v>
+        <f t="shared" si="6"/>
+        <v>406024518179792.81</v>
       </c>
       <c r="M41" s="64">
-        <f t="shared" si="8"/>
-        <v>523516308165498.19</v>
+        <f t="shared" si="6"/>
+        <v>411039801011830.94</v>
       </c>
       <c r="N41" s="64">
-        <f t="shared" si="8"/>
-        <v>535850241964573.5</v>
+        <f t="shared" si="6"/>
+        <v>416120286476322.69</v>
       </c>
       <c r="O41" s="64">
-        <f t="shared" si="8"/>
-        <v>548377407134918</v>
+        <f t="shared" si="6"/>
+        <v>420793335891148.44</v>
       </c>
       <c r="P41" s="64">
-        <f t="shared" si="8"/>
-        <v>560885355180585.19</v>
+        <f t="shared" si="6"/>
+        <v>425479109184856</v>
       </c>
       <c r="Q41" s="64">
-        <f t="shared" si="8"/>
-        <v>573376948646339.75</v>
+        <f t="shared" si="6"/>
+        <v>430178238629081.31</v>
       </c>
       <c r="R41" s="64">
-        <f t="shared" si="8"/>
-        <v>585855045420452.5</v>
+        <f t="shared" si="6"/>
+        <v>432568888838688.88</v>
       </c>
       <c r="S41" s="64">
-        <f t="shared" si="8"/>
-        <v>598312953850562.38</v>
+        <f t="shared" si="6"/>
+        <v>434399530869236.94</v>
       </c>
       <c r="T41" s="64">
-        <f t="shared" si="8"/>
-        <v>610762658039900</v>
+        <f t="shared" si="6"/>
+        <v>436259041457071.44</v>
       </c>
       <c r="U41" s="64">
-        <f t="shared" si="8"/>
-        <v>623206915471205.75</v>
+        <f t="shared" si="6"/>
+        <v>438147322625454.56</v>
       </c>
       <c r="V41" s="64">
-        <f t="shared" si="8"/>
-        <v>635648597334358.38</v>
+        <f t="shared" si="6"/>
+        <v>440064413539171.19</v>
       </c>
       <c r="W41" s="64">
-        <f t="shared" si="8"/>
-        <v>648090721843250.62</v>
+        <f t="shared" si="6"/>
+        <v>443158580392373.31</v>
       </c>
       <c r="X41" s="64">
-        <f t="shared" si="8"/>
-        <v>660544252717506.88</v>
+        <f t="shared" si="6"/>
+        <v>446855608950264.88</v>
       </c>
       <c r="Y41" s="64">
-        <f t="shared" si="8"/>
-        <v>673194373947774.88</v>
+        <f t="shared" si="6"/>
+        <v>450130817584451</v>
       </c>
       <c r="Z41" s="64">
-        <f t="shared" si="8"/>
-        <v>685858761094426</v>
+        <f t="shared" si="6"/>
+        <v>453432020240611.38</v>
       </c>
       <c r="AA41" s="64">
-        <f t="shared" si="8"/>
-        <v>698540182527301.5</v>
+        <f t="shared" si="6"/>
+        <v>456759743840300.81</v>
       </c>
       <c r="AB41" s="64">
-        <f t="shared" si="8"/>
-        <v>711241383708136.5</v>
+        <f t="shared" si="6"/>
+        <v>461822868044274.38</v>
       </c>
       <c r="AC41" s="64">
-        <f t="shared" si="8"/>
-        <v>723964736344253.5</v>
+        <f t="shared" si="6"/>
+        <v>466908914798611.25</v>
       </c>
       <c r="AD41" s="64">
-        <f t="shared" si="8"/>
-        <v>736713529411264.62</v>
+        <f t="shared" si="6"/>
+        <v>472019231257333</v>
       </c>
       <c r="AE41" s="64">
-        <f t="shared" si="8"/>
-        <v>749490630827695.5</v>
+        <f t="shared" si="6"/>
+        <v>477722264312581.12</v>
       </c>
       <c r="AF41" s="64">
-        <f t="shared" si="8"/>
-        <v>762299054940053.25</v>
+        <f t="shared" si="6"/>
+        <v>482883862311468.62</v>
       </c>
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.2">
@@ -24028,127 +23970,127 @@
         <v>153</v>
       </c>
       <c r="B42" s="64">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="C42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="D42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="V42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="X42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Y42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AA42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AF42" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -24259,123 +24201,123 @@
         <v>0</v>
       </c>
       <c r="C46" s="64">
-        <f t="shared" ref="C46:AF50" si="10">C25*C$34</f>
+        <f t="shared" ref="C46:AF50" si="8">C25*C$34</f>
         <v>0</v>
       </c>
       <c r="D46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="P46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Y46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Z46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AA46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AB46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AC46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF46" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -24384,128 +24326,128 @@
         <v>74</v>
       </c>
       <c r="B47" s="64">
-        <f t="shared" ref="B47:Q50" si="11">B26*B$34</f>
+        <f t="shared" ref="B47:Q50" si="9">B26*B$34</f>
         <v>157979422411178.94</v>
       </c>
       <c r="C47" s="64">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>174473309879167.41</v>
       </c>
       <c r="D47" s="64">
-        <f t="shared" si="11"/>
-        <v>191028463144402.19</v>
+        <f t="shared" si="9"/>
+        <v>186607969782382.97</v>
       </c>
       <c r="E47" s="64">
-        <f t="shared" si="11"/>
-        <v>207752670035952.03</v>
+        <f t="shared" si="9"/>
+        <v>193469673970980.34</v>
       </c>
       <c r="F47" s="64">
-        <f t="shared" si="11"/>
-        <v>224762272039822.75</v>
+        <f t="shared" si="9"/>
+        <v>201120610832671.03</v>
       </c>
       <c r="G47" s="64">
-        <f t="shared" si="11"/>
-        <v>242119137713583.41</v>
+        <f t="shared" si="9"/>
+        <v>210063927931785.03</v>
       </c>
       <c r="H47" s="64">
-        <f t="shared" si="11"/>
-        <v>259717016588631.19</v>
+        <f t="shared" si="9"/>
+        <v>218232016623467.28</v>
       </c>
       <c r="I47" s="64">
-        <f t="shared" si="11"/>
-        <v>276769231427356.72</v>
+        <f t="shared" si="9"/>
+        <v>225673373317690.84</v>
       </c>
       <c r="J47" s="64">
-        <f t="shared" si="11"/>
-        <v>293830565636684.25</v>
+        <f t="shared" si="9"/>
+        <v>233261811002373.88</v>
       </c>
       <c r="K47" s="64">
-        <f t="shared" si="11"/>
-        <v>311094029076771.5</v>
+        <f t="shared" si="9"/>
+        <v>240823377802959.56</v>
       </c>
       <c r="L47" s="64">
-        <f t="shared" si="11"/>
-        <v>328458780650970.75</v>
+        <f t="shared" si="9"/>
+        <v>247921429915083</v>
       </c>
       <c r="M47" s="64">
-        <f t="shared" si="11"/>
-        <v>346004915178361.31</v>
+        <f t="shared" si="9"/>
+        <v>254990578794488.03</v>
       </c>
       <c r="N47" s="64">
-        <f t="shared" si="11"/>
-        <v>363747039450784.62</v>
+        <f t="shared" si="9"/>
+        <v>261669336233182.22</v>
       </c>
       <c r="O47" s="64">
-        <f t="shared" si="11"/>
-        <v>381659987060398.81</v>
+        <f t="shared" si="9"/>
+        <v>268318536357613.72</v>
       </c>
       <c r="P47" s="64">
-        <f t="shared" si="11"/>
-        <v>399643904618942.81</v>
+        <f t="shared" si="9"/>
+        <v>274877027079370.41</v>
       </c>
       <c r="Q47" s="64">
-        <f t="shared" si="11"/>
-        <v>417784276337407.38</v>
+        <f t="shared" si="9"/>
+        <v>280624910143617.03</v>
       </c>
       <c r="R47" s="64">
-        <f t="shared" si="10"/>
-        <v>436028450789735.75</v>
+        <f t="shared" si="8"/>
+        <v>285110840881690.25</v>
       </c>
       <c r="S47" s="64">
-        <f t="shared" si="10"/>
-        <v>454410280373778.81</v>
+        <f t="shared" si="8"/>
+        <v>289133620874997.31</v>
       </c>
       <c r="T47" s="64">
-        <f t="shared" si="10"/>
-        <v>473281818214009.12</v>
+        <f t="shared" si="8"/>
+        <v>292906601658627.12</v>
       </c>
       <c r="U47" s="64">
-        <f t="shared" si="10"/>
-        <v>492218894860515.25</v>
+        <f t="shared" si="8"/>
+        <v>296972066565844.19</v>
       </c>
       <c r="V47" s="64">
-        <f t="shared" si="10"/>
-        <v>513306082815374.06</v>
+        <f t="shared" si="8"/>
+        <v>301749162853410.19</v>
       </c>
       <c r="W47" s="64">
-        <f t="shared" si="10"/>
-        <v>534539101156503.06</v>
+        <f t="shared" si="8"/>
+        <v>307254758932478.12</v>
       </c>
       <c r="X47" s="64">
-        <f t="shared" si="10"/>
-        <v>555617401761592.94</v>
+        <f t="shared" si="8"/>
+        <v>312508178462076.06</v>
       </c>
       <c r="Y47" s="64">
-        <f t="shared" si="10"/>
-        <v>577063164356548.12</v>
+        <f t="shared" si="8"/>
+        <v>317384740396101.44</v>
       </c>
       <c r="Z47" s="64">
-        <f t="shared" si="10"/>
-        <v>598709388574027</v>
+        <f t="shared" si="8"/>
+        <v>322214507305294.56</v>
       </c>
       <c r="AA47" s="64">
-        <f t="shared" si="10"/>
-        <v>620707439533960.25</v>
+        <f t="shared" si="8"/>
+        <v>327082005371441.44</v>
       </c>
       <c r="AB47" s="64">
-        <f t="shared" si="10"/>
-        <v>642384035129600.38</v>
+        <f t="shared" si="8"/>
+        <v>332528206420028.44</v>
       </c>
       <c r="AC47" s="64">
-        <f t="shared" si="10"/>
-        <v>664563004446702.62</v>
+        <f t="shared" si="8"/>
+        <v>337669850908054.31</v>
       </c>
       <c r="AD47" s="64">
-        <f t="shared" si="10"/>
-        <v>685986845247257.5</v>
+        <f t="shared" si="8"/>
+        <v>342767024324867.25</v>
       </c>
       <c r="AE47" s="64">
-        <f t="shared" si="10"/>
-        <v>707495539880403.38</v>
+        <f t="shared" si="8"/>
+        <v>347357487644507.69</v>
       </c>
       <c r="AF47" s="64">
-        <f t="shared" si="10"/>
-        <v>729035219022914.38</v>
+        <f t="shared" si="8"/>
+        <v>352328692600348.56</v>
       </c>
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.2">
@@ -24513,128 +24455,128 @@
         <v>76</v>
       </c>
       <c r="B48" s="64">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>179969356724899.38</v>
       </c>
       <c r="C48" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>186778931351007.28</v>
       </c>
       <c r="D48" s="64">
-        <f t="shared" si="10"/>
-        <v>194082784290907.62</v>
+        <f t="shared" si="8"/>
+        <v>189591612423018.84</v>
       </c>
       <c r="E48" s="64">
-        <f t="shared" si="10"/>
-        <v>201547963418261.31</v>
+        <f t="shared" si="8"/>
+        <v>187691540933255.84</v>
       </c>
       <c r="F48" s="64">
-        <f t="shared" si="10"/>
-        <v>208805240279238.16</v>
+        <f t="shared" si="8"/>
+        <v>186842022412829.41</v>
       </c>
       <c r="G48" s="64">
-        <f t="shared" si="10"/>
-        <v>215829288506856.09</v>
+        <f t="shared" si="8"/>
+        <v>187254706648201.91</v>
       </c>
       <c r="H48" s="64">
-        <f t="shared" si="10"/>
-        <v>222672333091115.09</v>
+        <f t="shared" si="8"/>
+        <v>187104537604077.91</v>
       </c>
       <c r="I48" s="64">
-        <f t="shared" si="10"/>
-        <v>228779960810428</v>
+        <f t="shared" si="8"/>
+        <v>186543660353118.22</v>
       </c>
       <c r="J48" s="64">
-        <f t="shared" si="10"/>
-        <v>234988568955614.66</v>
+        <f t="shared" si="8"/>
+        <v>186549207502187.34</v>
       </c>
       <c r="K48" s="64">
-        <f t="shared" si="10"/>
-        <v>241033545412734.12</v>
+        <f t="shared" si="8"/>
+        <v>186588321037151.81</v>
       </c>
       <c r="L48" s="64">
-        <f t="shared" si="10"/>
-        <v>246964410224841.19</v>
+        <f t="shared" si="8"/>
+        <v>186409294949371.66</v>
       </c>
       <c r="M48" s="64">
-        <f t="shared" si="10"/>
-        <v>252749291449460.31</v>
+        <f t="shared" si="8"/>
+        <v>186265238698624</v>
       </c>
       <c r="N48" s="64">
-        <f t="shared" si="10"/>
-        <v>258242183052632.53</v>
+        <f t="shared" si="8"/>
+        <v>185772125400166.03</v>
       </c>
       <c r="O48" s="64">
-        <f t="shared" si="10"/>
-        <v>263595657955679.44</v>
+        <f t="shared" si="8"/>
+        <v>185315735290053.41</v>
       </c>
       <c r="P48" s="64">
-        <f t="shared" si="10"/>
-        <v>268856261423541.88</v>
+        <f t="shared" si="8"/>
+        <v>184920648101070.28</v>
       </c>
       <c r="Q48" s="64">
-        <f t="shared" si="10"/>
-        <v>273989904193986.72</v>
+        <f t="shared" si="8"/>
+        <v>184038501685017.5</v>
       </c>
       <c r="R48" s="64">
-        <f t="shared" si="10"/>
-        <v>279021902130087.62</v>
+        <f t="shared" si="8"/>
+        <v>182447198105153.19</v>
       </c>
       <c r="S48" s="64">
-        <f t="shared" si="10"/>
-        <v>283848347762916.75</v>
+        <f t="shared" si="8"/>
+        <v>180607931010209.84</v>
       </c>
       <c r="T48" s="64">
-        <f t="shared" si="10"/>
-        <v>287916444698413.31</v>
+        <f t="shared" si="8"/>
+        <v>178186915560133.91</v>
       </c>
       <c r="U48" s="64">
-        <f t="shared" si="10"/>
-        <v>291877689696279.5</v>
+        <f t="shared" si="8"/>
+        <v>176099539450088.62</v>
       </c>
       <c r="V48" s="64">
-        <f t="shared" si="10"/>
-        <v>296850372138169.44</v>
+        <f t="shared" si="8"/>
+        <v>174504753175960.34</v>
       </c>
       <c r="W48" s="64">
-        <f t="shared" si="10"/>
-        <v>301718934909706.19</v>
+        <f t="shared" si="8"/>
+        <v>173428994081957.09</v>
       </c>
       <c r="X48" s="64">
-        <f t="shared" si="10"/>
-        <v>307182757127004.75</v>
+        <f t="shared" si="8"/>
+        <v>172775589066070.09</v>
       </c>
       <c r="Y48" s="64">
-        <f t="shared" si="10"/>
-        <v>312119379976430.69</v>
+        <f t="shared" si="8"/>
+        <v>171665658987036.88</v>
       </c>
       <c r="Z48" s="64">
-        <f t="shared" si="10"/>
-        <v>316957099207935.81</v>
+        <f t="shared" si="8"/>
+        <v>170580547937361.81</v>
       </c>
       <c r="AA48" s="64">
-        <f t="shared" si="10"/>
-        <v>321870844304427.25</v>
+        <f t="shared" si="8"/>
+        <v>169609955544815.22</v>
       </c>
       <c r="AB48" s="64">
-        <f t="shared" si="10"/>
-        <v>326428303072750.88</v>
+        <f t="shared" si="8"/>
+        <v>168974651002365.16</v>
       </c>
       <c r="AC48" s="64">
-        <f t="shared" si="10"/>
-        <v>330827099491843.75</v>
+        <f t="shared" si="8"/>
+        <v>168095931633693.56</v>
       </c>
       <c r="AD48" s="64">
-        <f t="shared" si="10"/>
-        <v>336745157893167.75</v>
+        <f t="shared" si="8"/>
+        <v>168261441930777.56</v>
       </c>
       <c r="AE48" s="64">
-        <f t="shared" si="10"/>
-        <v>342648123146145.88</v>
+        <f t="shared" si="8"/>
+        <v>168229175299494.84</v>
       </c>
       <c r="AF48" s="64">
-        <f t="shared" si="10"/>
-        <v>348558039833970.5</v>
+        <f t="shared" si="8"/>
+        <v>168451393383483.53</v>
       </c>
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.2">
@@ -24642,128 +24584,128 @@
         <v>152</v>
       </c>
       <c r="B49" s="64">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>11772238206051.732</v>
       </c>
       <c r="C49" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>12414346168059.471</v>
       </c>
       <c r="D49" s="64">
-        <f t="shared" si="10"/>
-        <v>13076796092052.904</v>
+        <f t="shared" si="8"/>
+        <v>12774192546121.102</v>
       </c>
       <c r="E49" s="64">
-        <f t="shared" si="10"/>
-        <v>13723595911826.078</v>
+        <f t="shared" si="8"/>
+        <v>12780098692888.035</v>
       </c>
       <c r="F49" s="64">
-        <f t="shared" si="10"/>
-        <v>14370203761231.777</v>
+        <f t="shared" si="8"/>
+        <v>12858671217457.768</v>
       </c>
       <c r="G49" s="64">
-        <f t="shared" si="10"/>
-        <v>15014839417223.707</v>
+        <f t="shared" si="8"/>
+        <v>13026959269027.893</v>
       </c>
       <c r="H49" s="64">
-        <f t="shared" si="10"/>
-        <v>15661093796781.688</v>
+        <f t="shared" si="8"/>
+        <v>13159523109778.975</v>
       </c>
       <c r="I49" s="64">
-        <f t="shared" si="10"/>
-        <v>16251633704706.131</v>
+        <f t="shared" si="8"/>
+        <v>13251332097683.461</v>
       </c>
       <c r="J49" s="64">
-        <f t="shared" si="10"/>
-        <v>16836180240740.457</v>
+        <f t="shared" si="8"/>
+        <v>13365654743262.67</v>
       </c>
       <c r="K49" s="64">
-        <f t="shared" si="10"/>
-        <v>17419668791489.736</v>
+        <f t="shared" si="8"/>
+        <v>13484873017412.055</v>
       </c>
       <c r="L49" s="64">
-        <f t="shared" si="10"/>
-        <v>18005700263806.824</v>
+        <f t="shared" si="8"/>
+        <v>13590743249969.443</v>
       </c>
       <c r="M49" s="64">
-        <f t="shared" si="10"/>
-        <v>18592011661124.887</v>
+        <f t="shared" si="8"/>
+        <v>13701504245915.947</v>
       </c>
       <c r="N49" s="64">
-        <f t="shared" si="10"/>
-        <v>19162180269682.93</v>
+        <f t="shared" si="8"/>
+        <v>13784730728033.689</v>
       </c>
       <c r="O49" s="64">
-        <f t="shared" si="10"/>
-        <v>19732326632881.312</v>
+        <f t="shared" si="8"/>
+        <v>13872423572207.469</v>
       </c>
       <c r="P49" s="64">
-        <f t="shared" si="10"/>
-        <v>20305961025646.301</v>
+        <f t="shared" si="8"/>
+        <v>13966539046907.943</v>
       </c>
       <c r="Q49" s="64">
-        <f t="shared" si="10"/>
-        <v>20880572585543.078</v>
+        <f t="shared" si="8"/>
+        <v>14025441208402.52</v>
       </c>
       <c r="R49" s="64">
-        <f t="shared" si="10"/>
-        <v>21458124872225.711</v>
+        <f t="shared" si="8"/>
+        <v>14031066126496.447</v>
       </c>
       <c r="S49" s="64">
-        <f t="shared" si="10"/>
-        <v>22011635597974.75</v>
+        <f t="shared" si="8"/>
+        <v>14005633623844.111</v>
       </c>
       <c r="T49" s="64">
-        <f t="shared" si="10"/>
-        <v>22582303485809.227</v>
+        <f t="shared" si="8"/>
+        <v>13975829024264.768</v>
       </c>
       <c r="U49" s="64">
-        <f t="shared" si="10"/>
-        <v>23157608794168.352</v>
+        <f t="shared" si="8"/>
+        <v>13971757305814.904</v>
       </c>
       <c r="V49" s="64">
-        <f t="shared" si="10"/>
-        <v>23827414547627.508</v>
+        <f t="shared" si="8"/>
+        <v>14007046932451.475</v>
       </c>
       <c r="W49" s="64">
-        <f t="shared" si="10"/>
-        <v>24504404055155.539</v>
+        <f t="shared" si="8"/>
+        <v>14085208630128.773</v>
       </c>
       <c r="X49" s="64">
-        <f t="shared" si="10"/>
-        <v>25131268266948.605</v>
+        <f t="shared" si="8"/>
+        <v>14135134795356.533</v>
       </c>
       <c r="Y49" s="64">
-        <f t="shared" si="10"/>
-        <v>25774941711731.934</v>
+        <f t="shared" si="8"/>
+        <v>14176217941452.564</v>
       </c>
       <c r="Z49" s="64">
-        <f t="shared" si="10"/>
-        <v>26420679822530.461</v>
+        <f t="shared" si="8"/>
+        <v>14219129504489.121</v>
       </c>
       <c r="AA49" s="64">
-        <f t="shared" si="10"/>
-        <v>26504500491545.223</v>
+        <f t="shared" si="8"/>
+        <v>13966555932778.793</v>
       </c>
       <c r="AB49" s="64">
-        <f t="shared" si="10"/>
-        <v>27725788017032.492</v>
+        <f t="shared" si="8"/>
+        <v>14352172620581.525</v>
       </c>
       <c r="AC49" s="64">
-        <f t="shared" si="10"/>
-        <v>28351565163994.234</v>
+        <f t="shared" si="8"/>
+        <v>14405660137380.854</v>
       </c>
       <c r="AD49" s="64">
-        <f t="shared" si="10"/>
-        <v>28938927915238.898</v>
+        <f t="shared" si="8"/>
+        <v>14459913156327.291</v>
       </c>
       <c r="AE49" s="64">
-        <f t="shared" si="10"/>
-        <v>29528333527227.195</v>
+        <f t="shared" si="8"/>
+        <v>14497459234980.578</v>
       </c>
       <c r="AF49" s="64">
-        <f t="shared" si="10"/>
-        <v>30121697941588.055</v>
+        <f t="shared" si="8"/>
+        <v>14557236986281.672</v>
       </c>
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.2">
@@ -24771,128 +24713,128 @@
         <v>153</v>
       </c>
       <c r="B50" s="64">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>185278982657869.91</v>
       </c>
       <c r="C50" s="64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>196333412601765.81</v>
       </c>
       <c r="D50" s="64">
-        <f t="shared" si="10"/>
-        <v>206811956472637.25</v>
+        <f t="shared" si="8"/>
+        <v>202026225248477.03</v>
       </c>
       <c r="E50" s="64">
-        <f t="shared" si="10"/>
-        <v>216975770633960.66</v>
+        <f t="shared" si="8"/>
+        <v>202058686402875.84</v>
       </c>
       <c r="F50" s="64">
-        <f t="shared" si="10"/>
-        <v>227062283919707.25</v>
+        <f t="shared" si="8"/>
+        <v>203178695537041.75</v>
       </c>
       <c r="G50" s="64">
-        <f t="shared" si="10"/>
-        <v>237036734362336.72</v>
+        <f t="shared" si="8"/>
+        <v>205654406150985.09</v>
       </c>
       <c r="H50" s="64">
-        <f t="shared" si="10"/>
-        <v>246949556523472.03</v>
+        <f t="shared" si="8"/>
+        <v>207503922662675.84</v>
       </c>
       <c r="I50" s="64">
-        <f t="shared" si="10"/>
-        <v>258199174057509.28</v>
+        <f t="shared" si="8"/>
+        <v>210531634231507.56</v>
       </c>
       <c r="J50" s="64">
-        <f t="shared" si="10"/>
-        <v>269344685166960.56</v>
+        <f t="shared" si="8"/>
+        <v>213823326752176.03</v>
       </c>
       <c r="K50" s="64">
-        <f t="shared" si="10"/>
-        <v>280452756719004.69</v>
+        <f t="shared" si="8"/>
+        <v>217103428142476.56</v>
       </c>
       <c r="L50" s="64">
-        <f t="shared" si="10"/>
-        <v>291571108860381.31</v>
+        <f t="shared" si="8"/>
+        <v>220078531885575.97</v>
       </c>
       <c r="M50" s="64">
-        <f t="shared" si="10"/>
-        <v>302653781711053.44</v>
+        <f t="shared" si="8"/>
+        <v>223042678260972</v>
       </c>
       <c r="N50" s="64">
-        <f t="shared" si="10"/>
-        <v>313848597226899.94</v>
+        <f t="shared" si="8"/>
+        <v>225773807638618.06</v>
       </c>
       <c r="O50" s="64">
-        <f t="shared" si="10"/>
-        <v>325012028351040.38</v>
+        <f t="shared" si="8"/>
+        <v>228493304780125.38</v>
       </c>
       <c r="P50" s="64">
-        <f t="shared" si="10"/>
-        <v>336193872931869</v>
+        <f t="shared" si="8"/>
+        <v>231235785772651.38</v>
       </c>
       <c r="Q50" s="64">
-        <f t="shared" si="10"/>
-        <v>347345246883062.88</v>
+        <f t="shared" si="8"/>
+        <v>233311146962962.97</v>
       </c>
       <c r="R50" s="64">
-        <f t="shared" si="10"/>
-        <v>358491522207950.94</v>
+        <f t="shared" si="8"/>
+        <v>234410894886660.16</v>
       </c>
       <c r="S50" s="64">
-        <f t="shared" si="10"/>
-        <v>369729736265329.56</v>
+        <f t="shared" si="8"/>
+        <v>235252814490948.62</v>
       </c>
       <c r="T50" s="64">
-        <f t="shared" si="10"/>
-        <v>381219433601768.25</v>
+        <f t="shared" si="8"/>
+        <v>235930653756974.16</v>
       </c>
       <c r="U50" s="64">
-        <f t="shared" si="10"/>
-        <v>392745806649037.19</v>
+        <f t="shared" si="8"/>
+        <v>236956636678252.44</v>
       </c>
       <c r="V50" s="64">
-        <f t="shared" si="10"/>
-        <v>401016130498829</v>
+        <f t="shared" si="8"/>
+        <v>235739037038178.03</v>
       </c>
       <c r="W50" s="64">
-        <f t="shared" si="10"/>
-        <v>409237559878635.38</v>
+        <f t="shared" si="8"/>
+        <v>235231038355436.06</v>
       </c>
       <c r="X50" s="64">
-        <f t="shared" si="10"/>
-        <v>417068572844453.75</v>
+        <f t="shared" si="8"/>
+        <v>234581097676497.38</v>
       </c>
       <c r="Y50" s="64">
-        <f t="shared" si="10"/>
-        <v>425042513955289.19</v>
+        <f t="shared" si="8"/>
+        <v>233773382675409.06</v>
       </c>
       <c r="Z50" s="64">
-        <f t="shared" si="10"/>
-        <v>432912832395506.56</v>
+        <f t="shared" si="8"/>
+        <v>232985815252854.44</v>
       </c>
       <c r="AA50" s="64">
-        <f t="shared" si="10"/>
-        <v>440917215670067.31</v>
+        <f t="shared" si="8"/>
+        <v>232341483150964.56</v>
       </c>
       <c r="AB50" s="64">
-        <f t="shared" si="10"/>
-        <v>448461873780616.25</v>
+        <f t="shared" si="8"/>
+        <v>232144969957024.88</v>
       </c>
       <c r="AC50" s="64">
-        <f t="shared" si="10"/>
-        <v>456258330897459.62</v>
+        <f t="shared" si="8"/>
+        <v>231828557320871.38</v>
       </c>
       <c r="AD50" s="64">
-        <f t="shared" si="10"/>
-        <v>463329068944335.69</v>
+        <f t="shared" si="8"/>
+        <v>231511620588027.81</v>
       </c>
       <c r="AE50" s="64">
-        <f t="shared" si="10"/>
-        <v>470328003446223.56</v>
+        <f t="shared" si="8"/>
+        <v>230915877821016.84</v>
       </c>
       <c r="AF50" s="64">
-        <f t="shared" si="10"/>
-        <v>477285043201527.06</v>
+        <f t="shared" si="8"/>
+        <v>230662677029886.28</v>
       </c>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.2">
@@ -26176,119 +26118,119 @@
       </c>
       <c r="E2" s="3">
         <f>'Electricity Share'!D47</f>
-        <v>191028463144402.19</v>
+        <v>186607969782382.97</v>
       </c>
       <c r="F2" s="3">
         <f>'Electricity Share'!E47</f>
-        <v>207752670035952.03</v>
+        <v>193469673970980.34</v>
       </c>
       <c r="G2" s="3">
         <f>'Electricity Share'!F47</f>
-        <v>224762272039822.75</v>
+        <v>201120610832671.03</v>
       </c>
       <c r="H2" s="3">
         <f>'Electricity Share'!G47</f>
-        <v>242119137713583.41</v>
+        <v>210063927931785.03</v>
       </c>
       <c r="I2" s="3">
         <f>'Electricity Share'!H47</f>
-        <v>259717016588631.19</v>
+        <v>218232016623467.28</v>
       </c>
       <c r="J2" s="3">
         <f>'Electricity Share'!I47</f>
-        <v>276769231427356.72</v>
+        <v>225673373317690.84</v>
       </c>
       <c r="K2" s="3">
         <f>'Electricity Share'!J47</f>
-        <v>293830565636684.25</v>
+        <v>233261811002373.88</v>
       </c>
       <c r="L2" s="3">
         <f>'Electricity Share'!K47</f>
-        <v>311094029076771.5</v>
+        <v>240823377802959.56</v>
       </c>
       <c r="M2" s="3">
         <f>'Electricity Share'!L47</f>
-        <v>328458780650970.75</v>
+        <v>247921429915083</v>
       </c>
       <c r="N2" s="3">
         <f>'Electricity Share'!M47</f>
-        <v>346004915178361.31</v>
+        <v>254990578794488.03</v>
       </c>
       <c r="O2" s="3">
         <f>'Electricity Share'!N47</f>
-        <v>363747039450784.62</v>
+        <v>261669336233182.22</v>
       </c>
       <c r="P2" s="3">
         <f>'Electricity Share'!O47</f>
-        <v>381659987060398.81</v>
+        <v>268318536357613.72</v>
       </c>
       <c r="Q2" s="3">
         <f>'Electricity Share'!P47</f>
-        <v>399643904618942.81</v>
+        <v>274877027079370.41</v>
       </c>
       <c r="R2" s="3">
         <f>'Electricity Share'!Q47</f>
-        <v>417784276337407.38</v>
+        <v>280624910143617.03</v>
       </c>
       <c r="S2" s="3">
         <f>'Electricity Share'!R47</f>
-        <v>436028450789735.75</v>
+        <v>285110840881690.25</v>
       </c>
       <c r="T2" s="3">
         <f>'Electricity Share'!S47</f>
-        <v>454410280373778.81</v>
+        <v>289133620874997.31</v>
       </c>
       <c r="U2" s="3">
         <f>'Electricity Share'!T47</f>
-        <v>473281818214009.12</v>
+        <v>292906601658627.12</v>
       </c>
       <c r="V2" s="3">
         <f>'Electricity Share'!U47</f>
-        <v>492218894860515.25</v>
+        <v>296972066565844.19</v>
       </c>
       <c r="W2" s="3">
         <f>'Electricity Share'!V47</f>
-        <v>513306082815374.06</v>
+        <v>301749162853410.19</v>
       </c>
       <c r="X2" s="3">
         <f>'Electricity Share'!W47</f>
-        <v>534539101156503.06</v>
+        <v>307254758932478.12</v>
       </c>
       <c r="Y2" s="3">
         <f>'Electricity Share'!X47</f>
-        <v>555617401761592.94</v>
+        <v>312508178462076.06</v>
       </c>
       <c r="Z2" s="3">
         <f>'Electricity Share'!Y47</f>
-        <v>577063164356548.12</v>
+        <v>317384740396101.44</v>
       </c>
       <c r="AA2" s="3">
         <f>'Electricity Share'!Z47</f>
-        <v>598709388574027</v>
+        <v>322214507305294.56</v>
       </c>
       <c r="AB2" s="3">
         <f>'Electricity Share'!AA47</f>
-        <v>620707439533960.25</v>
+        <v>327082005371441.44</v>
       </c>
       <c r="AC2" s="3">
         <f>'Electricity Share'!AB47</f>
-        <v>642384035129600.38</v>
+        <v>332528206420028.44</v>
       </c>
       <c r="AD2" s="3">
         <f>'Electricity Share'!AC47</f>
-        <v>664563004446702.62</v>
+        <v>337669850908054.31</v>
       </c>
       <c r="AE2" s="3">
         <f>'Electricity Share'!AD47</f>
-        <v>685986845247257.5</v>
+        <v>342767024324867.25</v>
       </c>
       <c r="AF2" s="3">
         <f>'Electricity Share'!AE47</f>
-        <v>707495539880403.38</v>
+        <v>347357487644507.69</v>
       </c>
       <c r="AG2" s="3">
         <f>'Electricity Share'!AF47</f>
-        <v>729035219022914.38</v>
+        <v>352328692600348.56</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.2">
@@ -27338,119 +27280,119 @@
       </c>
       <c r="E2" s="3">
         <f>'Electricity Share'!D48</f>
-        <v>194082784290907.62</v>
+        <v>189591612423018.84</v>
       </c>
       <c r="F2" s="3">
         <f>'Electricity Share'!E48</f>
-        <v>201547963418261.31</v>
+        <v>187691540933255.84</v>
       </c>
       <c r="G2" s="3">
         <f>'Electricity Share'!F48</f>
-        <v>208805240279238.16</v>
+        <v>186842022412829.41</v>
       </c>
       <c r="H2" s="3">
         <f>'Electricity Share'!G48</f>
-        <v>215829288506856.09</v>
+        <v>187254706648201.91</v>
       </c>
       <c r="I2" s="3">
         <f>'Electricity Share'!H48</f>
-        <v>222672333091115.09</v>
+        <v>187104537604077.91</v>
       </c>
       <c r="J2" s="3">
         <f>'Electricity Share'!I48</f>
-        <v>228779960810428</v>
+        <v>186543660353118.22</v>
       </c>
       <c r="K2" s="3">
         <f>'Electricity Share'!J48</f>
-        <v>234988568955614.66</v>
+        <v>186549207502187.34</v>
       </c>
       <c r="L2" s="3">
         <f>'Electricity Share'!K48</f>
-        <v>241033545412734.12</v>
+        <v>186588321037151.81</v>
       </c>
       <c r="M2" s="3">
         <f>'Electricity Share'!L48</f>
-        <v>246964410224841.19</v>
+        <v>186409294949371.66</v>
       </c>
       <c r="N2" s="3">
         <f>'Electricity Share'!M48</f>
-        <v>252749291449460.31</v>
+        <v>186265238698624</v>
       </c>
       <c r="O2" s="3">
         <f>'Electricity Share'!N48</f>
-        <v>258242183052632.53</v>
+        <v>185772125400166.03</v>
       </c>
       <c r="P2" s="3">
         <f>'Electricity Share'!O48</f>
-        <v>263595657955679.44</v>
+        <v>185315735290053.41</v>
       </c>
       <c r="Q2" s="3">
         <f>'Electricity Share'!P48</f>
-        <v>268856261423541.88</v>
+        <v>184920648101070.28</v>
       </c>
       <c r="R2" s="3">
         <f>'Electricity Share'!Q48</f>
-        <v>273989904193986.72</v>
+        <v>184038501685017.5</v>
       </c>
       <c r="S2" s="3">
         <f>'Electricity Share'!R48</f>
-        <v>279021902130087.62</v>
+        <v>182447198105153.19</v>
       </c>
       <c r="T2" s="3">
         <f>'Electricity Share'!S48</f>
-        <v>283848347762916.75</v>
+        <v>180607931010209.84</v>
       </c>
       <c r="U2" s="3">
         <f>'Electricity Share'!T48</f>
-        <v>287916444698413.31</v>
+        <v>178186915560133.91</v>
       </c>
       <c r="V2" s="3">
         <f>'Electricity Share'!U48</f>
-        <v>291877689696279.5</v>
+        <v>176099539450088.62</v>
       </c>
       <c r="W2" s="3">
         <f>'Electricity Share'!V48</f>
-        <v>296850372138169.44</v>
+        <v>174504753175960.34</v>
       </c>
       <c r="X2" s="3">
         <f>'Electricity Share'!W48</f>
-        <v>301718934909706.19</v>
+        <v>173428994081957.09</v>
       </c>
       <c r="Y2" s="3">
         <f>'Electricity Share'!X48</f>
-        <v>307182757127004.75</v>
+        <v>172775589066070.09</v>
       </c>
       <c r="Z2" s="3">
         <f>'Electricity Share'!Y48</f>
-        <v>312119379976430.69</v>
+        <v>171665658987036.88</v>
       </c>
       <c r="AA2" s="3">
         <f>'Electricity Share'!Z48</f>
-        <v>316957099207935.81</v>
+        <v>170580547937361.81</v>
       </c>
       <c r="AB2" s="3">
         <f>'Electricity Share'!AA48</f>
-        <v>321870844304427.25</v>
+        <v>169609955544815.22</v>
       </c>
       <c r="AC2" s="3">
         <f>'Electricity Share'!AB48</f>
-        <v>326428303072750.88</v>
+        <v>168974651002365.16</v>
       </c>
       <c r="AD2" s="3">
         <f>'Electricity Share'!AC48</f>
-        <v>330827099491843.75</v>
+        <v>168095931633693.56</v>
       </c>
       <c r="AE2" s="3">
         <f>'Electricity Share'!AD48</f>
-        <v>336745157893167.75</v>
+        <v>168261441930777.56</v>
       </c>
       <c r="AF2" s="3">
         <f>'Electricity Share'!AE48</f>
-        <v>342648123146145.88</v>
+        <v>168229175299494.84</v>
       </c>
       <c r="AG2" s="3">
         <f>'Electricity Share'!AF48</f>
-        <v>348558039833970.5</v>
+        <v>168451393383483.53</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.2">
@@ -28500,119 +28442,119 @@
       </c>
       <c r="E2" s="3">
         <f>'Electricity Share'!D49</f>
-        <v>13076796092052.904</v>
+        <v>12774192546121.102</v>
       </c>
       <c r="F2" s="3">
         <f>'Electricity Share'!E49</f>
-        <v>13723595911826.078</v>
+        <v>12780098692888.035</v>
       </c>
       <c r="G2" s="3">
         <f>'Electricity Share'!F49</f>
-        <v>14370203761231.777</v>
+        <v>12858671217457.768</v>
       </c>
       <c r="H2" s="3">
         <f>'Electricity Share'!G49</f>
-        <v>15014839417223.707</v>
+        <v>13026959269027.893</v>
       </c>
       <c r="I2" s="3">
         <f>'Electricity Share'!H49</f>
-        <v>15661093796781.688</v>
+        <v>13159523109778.975</v>
       </c>
       <c r="J2" s="3">
         <f>'Electricity Share'!I49</f>
-        <v>16251633704706.131</v>
+        <v>13251332097683.461</v>
       </c>
       <c r="K2" s="3">
         <f>'Electricity Share'!J49</f>
-        <v>16836180240740.457</v>
+        <v>13365654743262.67</v>
       </c>
       <c r="L2" s="3">
         <f>'Electricity Share'!K49</f>
-        <v>17419668791489.736</v>
+        <v>13484873017412.055</v>
       </c>
       <c r="M2" s="3">
         <f>'Electricity Share'!L49</f>
-        <v>18005700263806.824</v>
+        <v>13590743249969.443</v>
       </c>
       <c r="N2" s="3">
         <f>'Electricity Share'!M49</f>
-        <v>18592011661124.887</v>
+        <v>13701504245915.947</v>
       </c>
       <c r="O2" s="3">
         <f>'Electricity Share'!N49</f>
-        <v>19162180269682.93</v>
+        <v>13784730728033.689</v>
       </c>
       <c r="P2" s="3">
         <f>'Electricity Share'!O49</f>
-        <v>19732326632881.312</v>
+        <v>13872423572207.469</v>
       </c>
       <c r="Q2" s="3">
         <f>'Electricity Share'!P49</f>
-        <v>20305961025646.301</v>
+        <v>13966539046907.943</v>
       </c>
       <c r="R2" s="3">
         <f>'Electricity Share'!Q49</f>
-        <v>20880572585543.078</v>
+        <v>14025441208402.52</v>
       </c>
       <c r="S2" s="3">
         <f>'Electricity Share'!R49</f>
-        <v>21458124872225.711</v>
+        <v>14031066126496.447</v>
       </c>
       <c r="T2" s="3">
         <f>'Electricity Share'!S49</f>
-        <v>22011635597974.75</v>
+        <v>14005633623844.111</v>
       </c>
       <c r="U2" s="3">
         <f>'Electricity Share'!T49</f>
-        <v>22582303485809.227</v>
+        <v>13975829024264.768</v>
       </c>
       <c r="V2" s="3">
         <f>'Electricity Share'!U49</f>
-        <v>23157608794168.352</v>
+        <v>13971757305814.904</v>
       </c>
       <c r="W2" s="3">
         <f>'Electricity Share'!V49</f>
-        <v>23827414547627.508</v>
+        <v>14007046932451.475</v>
       </c>
       <c r="X2" s="3">
         <f>'Electricity Share'!W49</f>
-        <v>24504404055155.539</v>
+        <v>14085208630128.773</v>
       </c>
       <c r="Y2" s="3">
         <f>'Electricity Share'!X49</f>
-        <v>25131268266948.605</v>
+        <v>14135134795356.533</v>
       </c>
       <c r="Z2" s="3">
         <f>'Electricity Share'!Y49</f>
-        <v>25774941711731.934</v>
+        <v>14176217941452.564</v>
       </c>
       <c r="AA2" s="3">
         <f>'Electricity Share'!Z49</f>
-        <v>26420679822530.461</v>
+        <v>14219129504489.121</v>
       </c>
       <c r="AB2" s="3">
         <f>'Electricity Share'!AA49</f>
-        <v>26504500491545.223</v>
+        <v>13966555932778.793</v>
       </c>
       <c r="AC2" s="3">
         <f>'Electricity Share'!AB49</f>
-        <v>27725788017032.492</v>
+        <v>14352172620581.525</v>
       </c>
       <c r="AD2" s="3">
         <f>'Electricity Share'!AC49</f>
-        <v>28351565163994.234</v>
+        <v>14405660137380.854</v>
       </c>
       <c r="AE2" s="3">
         <f>'Electricity Share'!AD49</f>
-        <v>28938927915238.898</v>
+        <v>14459913156327.291</v>
       </c>
       <c r="AF2" s="3">
         <f>'Electricity Share'!AE49</f>
-        <v>29528333527227.195</v>
+        <v>14497459234980.578</v>
       </c>
       <c r="AG2" s="3">
         <f>'Electricity Share'!AF49</f>
-        <v>30121697941588.055</v>
+        <v>14557236986281.672</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.2">
@@ -30128,119 +30070,119 @@
       </c>
       <c r="E2" s="3">
         <f>'Electricity Share'!D50</f>
-        <v>206811956472637.25</v>
+        <v>202026225248477.03</v>
       </c>
       <c r="F2" s="3">
         <f>'Electricity Share'!E50</f>
-        <v>216975770633960.66</v>
+        <v>202058686402875.84</v>
       </c>
       <c r="G2" s="3">
         <f>'Electricity Share'!F50</f>
-        <v>227062283919707.25</v>
+        <v>203178695537041.75</v>
       </c>
       <c r="H2" s="3">
         <f>'Electricity Share'!G50</f>
-        <v>237036734362336.72</v>
+        <v>205654406150985.09</v>
       </c>
       <c r="I2" s="3">
         <f>'Electricity Share'!H50</f>
-        <v>246949556523472.03</v>
+        <v>207503922662675.84</v>
       </c>
       <c r="J2" s="3">
         <f>'Electricity Share'!I50</f>
-        <v>258199174057509.28</v>
+        <v>210531634231507.56</v>
       </c>
       <c r="K2" s="3">
         <f>'Electricity Share'!J50</f>
-        <v>269344685166960.56</v>
+        <v>213823326752176.03</v>
       </c>
       <c r="L2" s="3">
         <f>'Electricity Share'!K50</f>
-        <v>280452756719004.69</v>
+        <v>217103428142476.56</v>
       </c>
       <c r="M2" s="3">
         <f>'Electricity Share'!L50</f>
-        <v>291571108860381.31</v>
+        <v>220078531885575.97</v>
       </c>
       <c r="N2" s="3">
         <f>'Electricity Share'!M50</f>
-        <v>302653781711053.44</v>
+        <v>223042678260972</v>
       </c>
       <c r="O2" s="3">
         <f>'Electricity Share'!N50</f>
-        <v>313848597226899.94</v>
+        <v>225773807638618.06</v>
       </c>
       <c r="P2" s="3">
         <f>'Electricity Share'!O50</f>
-        <v>325012028351040.38</v>
+        <v>228493304780125.38</v>
       </c>
       <c r="Q2" s="3">
         <f>'Electricity Share'!P50</f>
-        <v>336193872931869</v>
+        <v>231235785772651.38</v>
       </c>
       <c r="R2" s="3">
         <f>'Electricity Share'!Q50</f>
-        <v>347345246883062.88</v>
+        <v>233311146962962.97</v>
       </c>
       <c r="S2" s="3">
         <f>'Electricity Share'!R50</f>
-        <v>358491522207950.94</v>
+        <v>234410894886660.16</v>
       </c>
       <c r="T2" s="3">
         <f>'Electricity Share'!S50</f>
-        <v>369729736265329.56</v>
+        <v>235252814490948.62</v>
       </c>
       <c r="U2" s="3">
         <f>'Electricity Share'!T50</f>
-        <v>381219433601768.25</v>
+        <v>235930653756974.16</v>
       </c>
       <c r="V2" s="3">
         <f>'Electricity Share'!U50</f>
-        <v>392745806649037.19</v>
+        <v>236956636678252.44</v>
       </c>
       <c r="W2" s="3">
         <f>'Electricity Share'!V50</f>
-        <v>401016130498829</v>
+        <v>235739037038178.03</v>
       </c>
       <c r="X2" s="3">
         <f>'Electricity Share'!W50</f>
-        <v>409237559878635.38</v>
+        <v>235231038355436.06</v>
       </c>
       <c r="Y2" s="3">
         <f>'Electricity Share'!X50</f>
-        <v>417068572844453.75</v>
+        <v>234581097676497.38</v>
       </c>
       <c r="Z2" s="3">
         <f>'Electricity Share'!Y50</f>
-        <v>425042513955289.19</v>
+        <v>233773382675409.06</v>
       </c>
       <c r="AA2" s="3">
         <f>'Electricity Share'!Z50</f>
-        <v>432912832395506.56</v>
+        <v>232985815252854.44</v>
       </c>
       <c r="AB2" s="3">
         <f>'Electricity Share'!AA50</f>
-        <v>440917215670067.31</v>
+        <v>232341483150964.56</v>
       </c>
       <c r="AC2" s="3">
         <f>'Electricity Share'!AB50</f>
-        <v>448461873780616.25</v>
+        <v>232144969957024.88</v>
       </c>
       <c r="AD2" s="3">
         <f>'Electricity Share'!AC50</f>
-        <v>456258330897459.62</v>
+        <v>231828557320871.38</v>
       </c>
       <c r="AE2" s="3">
         <f>'Electricity Share'!AD50</f>
-        <v>463329068944335.69</v>
+        <v>231511620588027.81</v>
       </c>
       <c r="AF2" s="3">
         <f>'Electricity Share'!AE50</f>
-        <v>470328003446223.56</v>
+        <v>230915877821016.84</v>
       </c>
       <c r="AG2" s="3">
         <f>'Electricity Share'!AF50</f>
-        <v>477285043201527.06</v>
+        <v>230662677029886.28</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.2">

--- a/InputData/bldgs/BCEU/BAU Components Energy Use.xlsx
+++ b/InputData/bldgs/BCEU/BAU Components Energy Use.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-brazil-cpl/InputData/bldgs/BCEU/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084D3B1F-69A3-0C4A-A770-C27B0224F50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BFACC75-CD01-9349-8E43-CA6E50B053F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" tabRatio="905" firstSheet="17" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" tabRatio="905" firstSheet="17" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
